--- a/Results/Results.out/Bovines/Data/reg_out_bv_lon_coefs.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_lon_coefs.xlsx
@@ -2915,12 +2915,12 @@
       <c r="CI14"/>
       <c r="CJ14"/>
       <c r="CK14" t="n">
-        <v>2.6</v>
+        <v>59.2</v>
       </c>
       <c r="CL14"/>
       <c r="CM14"/>
       <c r="CN14" t="n">
-        <v>2.6</v>
+        <v>59.2</v>
       </c>
       <c r="CO14"/>
       <c r="CP14"/>
@@ -3079,12 +3079,12 @@
       <c r="CI15"/>
       <c r="CJ15"/>
       <c r="CK15" t="n">
-        <v>2.6</v>
+        <v>59.2</v>
       </c>
       <c r="CL15"/>
       <c r="CM15"/>
       <c r="CN15" t="n">
-        <v>2.6</v>
+        <v>59.2</v>
       </c>
       <c r="CO15"/>
       <c r="CP15"/>
@@ -3243,12 +3243,12 @@
       <c r="CI16"/>
       <c r="CJ16"/>
       <c r="CK16" t="n">
-        <v>2.6</v>
+        <v>59.2</v>
       </c>
       <c r="CL16"/>
       <c r="CM16"/>
       <c r="CN16" t="n">
-        <v>2.6</v>
+        <v>59.2</v>
       </c>
       <c r="CO16"/>
       <c r="CP16"/>
@@ -3411,15 +3411,15 @@
       <c r="CI17"/>
       <c r="CJ17"/>
       <c r="CK17" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="CL17"/>
       <c r="CM17"/>
       <c r="CN17" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="CO17" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="CP17"/>
       <c r="CQ17"/>
@@ -3581,15 +3581,15 @@
       <c r="CI18"/>
       <c r="CJ18"/>
       <c r="CK18" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="CL18"/>
       <c r="CM18"/>
       <c r="CN18" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="CO18" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="CP18"/>
       <c r="CQ18"/>
@@ -3751,15 +3751,15 @@
       <c r="CI19"/>
       <c r="CJ19"/>
       <c r="CK19" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="CL19"/>
       <c r="CM19"/>
       <c r="CN19" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="CO19" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="CP19"/>
       <c r="CQ19"/>
@@ -3917,12 +3917,12 @@
       <c r="CI20"/>
       <c r="CJ20"/>
       <c r="CK20" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="CL20"/>
       <c r="CM20"/>
       <c r="CN20" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="CO20"/>
       <c r="CP20"/>
@@ -4081,12 +4081,12 @@
       <c r="CI21"/>
       <c r="CJ21"/>
       <c r="CK21" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="CL21"/>
       <c r="CM21"/>
       <c r="CN21" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="CO21"/>
       <c r="CP21"/>
@@ -4245,12 +4245,12 @@
       <c r="CI22"/>
       <c r="CJ22"/>
       <c r="CK22" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="CL22"/>
       <c r="CM22"/>
       <c r="CN22" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="CO22"/>
       <c r="CP22"/>
@@ -4413,7 +4413,7 @@
       <c r="CI23"/>
       <c r="CJ23"/>
       <c r="CK23" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="CL23"/>
       <c r="CM23"/>
@@ -4421,7 +4421,7 @@
         <v>1</v>
       </c>
       <c r="CO23" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="CP23"/>
       <c r="CQ23"/>
@@ -4583,7 +4583,7 @@
       <c r="CI24"/>
       <c r="CJ24"/>
       <c r="CK24" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="CL24"/>
       <c r="CM24"/>
@@ -4591,7 +4591,7 @@
         <v>1</v>
       </c>
       <c r="CO24" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="CP24"/>
       <c r="CQ24"/>
@@ -4753,7 +4753,7 @@
       <c r="CI25"/>
       <c r="CJ25"/>
       <c r="CK25" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="CL25"/>
       <c r="CM25"/>
@@ -4761,7 +4761,7 @@
         <v>1</v>
       </c>
       <c r="CO25" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="CP25"/>
       <c r="CQ25"/>
@@ -6647,12 +6647,12 @@
       <c r="CI38"/>
       <c r="CJ38"/>
       <c r="CK38" t="n">
-        <v>1.2</v>
+        <v>14.4</v>
       </c>
       <c r="CL38"/>
       <c r="CM38"/>
       <c r="CN38" t="n">
-        <v>1.2</v>
+        <v>14.4</v>
       </c>
       <c r="CO38"/>
       <c r="CP38"/>
@@ -6811,12 +6811,12 @@
       <c r="CI39"/>
       <c r="CJ39"/>
       <c r="CK39" t="n">
-        <v>1.2</v>
+        <v>14.4</v>
       </c>
       <c r="CL39"/>
       <c r="CM39"/>
       <c r="CN39" t="n">
-        <v>1.2</v>
+        <v>14.4</v>
       </c>
       <c r="CO39"/>
       <c r="CP39"/>
@@ -6975,12 +6975,12 @@
       <c r="CI40"/>
       <c r="CJ40"/>
       <c r="CK40" t="n">
-        <v>1.2</v>
+        <v>14.4</v>
       </c>
       <c r="CL40"/>
       <c r="CM40"/>
       <c r="CN40" t="n">
-        <v>1.2</v>
+        <v>14.4</v>
       </c>
       <c r="CO40"/>
       <c r="CP40"/>
@@ -7143,15 +7143,15 @@
       <c r="CI41"/>
       <c r="CJ41"/>
       <c r="CK41" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="CL41"/>
       <c r="CM41"/>
       <c r="CN41" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="CO41" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="CP41"/>
       <c r="CQ41"/>
@@ -7313,15 +7313,15 @@
       <c r="CI42"/>
       <c r="CJ42"/>
       <c r="CK42" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="CL42"/>
       <c r="CM42"/>
       <c r="CN42" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="CO42" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="CP42"/>
       <c r="CQ42"/>
@@ -7483,15 +7483,15 @@
       <c r="CI43"/>
       <c r="CJ43"/>
       <c r="CK43" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="CL43"/>
       <c r="CM43"/>
       <c r="CN43" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="CO43" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="CP43"/>
       <c r="CQ43"/>
@@ -7649,12 +7649,12 @@
       <c r="CI44"/>
       <c r="CJ44"/>
       <c r="CK44" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="CL44"/>
       <c r="CM44"/>
       <c r="CN44" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="CO44"/>
       <c r="CP44"/>
@@ -7813,12 +7813,12 @@
       <c r="CI45"/>
       <c r="CJ45"/>
       <c r="CK45" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="CL45"/>
       <c r="CM45"/>
       <c r="CN45" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="CO45"/>
       <c r="CP45"/>
@@ -7977,12 +7977,12 @@
       <c r="CI46"/>
       <c r="CJ46"/>
       <c r="CK46" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="CL46"/>
       <c r="CM46"/>
       <c r="CN46" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="CO46"/>
       <c r="CP46"/>
@@ -8145,7 +8145,7 @@
       <c r="CI47"/>
       <c r="CJ47"/>
       <c r="CK47" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="CL47"/>
       <c r="CM47"/>
@@ -8153,7 +8153,7 @@
         <v>1.2</v>
       </c>
       <c r="CO47" t="n">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="CP47"/>
       <c r="CQ47"/>
@@ -8315,7 +8315,7 @@
       <c r="CI48"/>
       <c r="CJ48"/>
       <c r="CK48" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="CL48"/>
       <c r="CM48"/>
@@ -8323,7 +8323,7 @@
         <v>1.2</v>
       </c>
       <c r="CO48" t="n">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="CP48"/>
       <c r="CQ48"/>
@@ -8485,7 +8485,7 @@
       <c r="CI49"/>
       <c r="CJ49"/>
       <c r="CK49" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="CL49"/>
       <c r="CM49"/>
@@ -8493,7 +8493,7 @@
         <v>1.2</v>
       </c>
       <c r="CO49" t="n">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="CP49"/>
       <c r="CQ49"/>
@@ -10400,7 +10400,7 @@
       <c r="CL62"/>
       <c r="CM62"/>
       <c r="CN62" t="n">
-        <v>415.2</v>
+        <v>579.6</v>
       </c>
       <c r="CO62"/>
       <c r="CP62"/>
@@ -10568,7 +10568,7 @@
       <c r="CL63"/>
       <c r="CM63"/>
       <c r="CN63" t="n">
-        <v>415.2</v>
+        <v>579.6</v>
       </c>
       <c r="CO63"/>
       <c r="CP63"/>
@@ -10736,7 +10736,7 @@
       <c r="CL64"/>
       <c r="CM64"/>
       <c r="CN64" t="n">
-        <v>415.2</v>
+        <v>579.6</v>
       </c>
       <c r="CO64"/>
       <c r="CP64"/>
@@ -10903,15 +10903,15 @@
       <c r="CI65"/>
       <c r="CJ65"/>
       <c r="CK65" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="CL65"/>
       <c r="CM65"/>
       <c r="CN65" t="n">
-        <v>22.3</v>
+        <v>31.8</v>
       </c>
       <c r="CO65" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="CP65"/>
       <c r="CQ65"/>
@@ -11077,15 +11077,15 @@
       <c r="CI66"/>
       <c r="CJ66"/>
       <c r="CK66" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="CL66"/>
       <c r="CM66"/>
       <c r="CN66" t="n">
-        <v>22.3</v>
+        <v>31.8</v>
       </c>
       <c r="CO66" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="CP66"/>
       <c r="CQ66"/>
@@ -11251,15 +11251,15 @@
       <c r="CI67"/>
       <c r="CJ67"/>
       <c r="CK67" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="CL67"/>
       <c r="CM67"/>
       <c r="CN67" t="n">
-        <v>22.3</v>
+        <v>31.8</v>
       </c>
       <c r="CO67" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="CP67"/>
       <c r="CQ67"/>
@@ -11421,12 +11421,12 @@
       <c r="CI68"/>
       <c r="CJ68"/>
       <c r="CK68" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="CL68"/>
       <c r="CM68"/>
       <c r="CN68" t="n">
-        <v>34.1</v>
+        <v>36.9</v>
       </c>
       <c r="CO68"/>
       <c r="CP68"/>
@@ -11589,12 +11589,12 @@
       <c r="CI69"/>
       <c r="CJ69"/>
       <c r="CK69" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="CL69"/>
       <c r="CM69"/>
       <c r="CN69" t="n">
-        <v>34.1</v>
+        <v>36.9</v>
       </c>
       <c r="CO69"/>
       <c r="CP69"/>
@@ -11757,12 +11757,12 @@
       <c r="CI70"/>
       <c r="CJ70"/>
       <c r="CK70" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="CL70"/>
       <c r="CM70"/>
       <c r="CN70" t="n">
-        <v>34.1</v>
+        <v>36.9</v>
       </c>
       <c r="CO70"/>
       <c r="CP70"/>
@@ -11929,15 +11929,15 @@
       <c r="CI71"/>
       <c r="CJ71"/>
       <c r="CK71" t="n">
-        <v>7.5</v>
+        <v>9.6</v>
       </c>
       <c r="CL71"/>
       <c r="CM71"/>
       <c r="CN71" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="CO71" t="n">
-        <v>7.9</v>
+        <v>12.2</v>
       </c>
       <c r="CP71"/>
       <c r="CQ71"/>
@@ -12103,15 +12103,15 @@
       <c r="CI72"/>
       <c r="CJ72"/>
       <c r="CK72" t="n">
-        <v>7.5</v>
+        <v>9.6</v>
       </c>
       <c r="CL72"/>
       <c r="CM72"/>
       <c r="CN72" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="CO72" t="n">
-        <v>7.9</v>
+        <v>12.2</v>
       </c>
       <c r="CP72"/>
       <c r="CQ72"/>
@@ -12277,15 +12277,15 @@
       <c r="CI73"/>
       <c r="CJ73"/>
       <c r="CK73" t="n">
-        <v>7.5</v>
+        <v>9.6</v>
       </c>
       <c r="CL73"/>
       <c r="CM73"/>
       <c r="CN73" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="CO73" t="n">
-        <v>7.9</v>
+        <v>12.2</v>
       </c>
       <c r="CP73"/>
       <c r="CQ73"/>
@@ -14211,16 +14211,16 @@
       <c r="CI86"/>
       <c r="CJ86"/>
       <c r="CK86" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="CL86"/>
       <c r="CM86"/>
       <c r="CN86" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="CO86"/>
       <c r="CP86" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="CQ86"/>
       <c r="CR86"/>
@@ -14381,16 +14381,16 @@
       <c r="CI87"/>
       <c r="CJ87"/>
       <c r="CK87" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="CL87"/>
       <c r="CM87"/>
       <c r="CN87" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="CO87"/>
       <c r="CP87" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="CQ87"/>
       <c r="CR87"/>
@@ -14551,16 +14551,16 @@
       <c r="CI88"/>
       <c r="CJ88"/>
       <c r="CK88" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="CL88"/>
       <c r="CM88"/>
       <c r="CN88" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="CO88"/>
       <c r="CP88" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="CQ88"/>
       <c r="CR88"/>
@@ -14725,19 +14725,19 @@
       <c r="CI89"/>
       <c r="CJ89"/>
       <c r="CK89" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="CL89"/>
       <c r="CM89"/>
       <c r="CN89" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="CO89" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="CP89"/>
       <c r="CQ89" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="CR89"/>
       <c r="CS89"/>
@@ -14901,19 +14901,19 @@
       <c r="CI90"/>
       <c r="CJ90"/>
       <c r="CK90" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="CL90"/>
       <c r="CM90"/>
       <c r="CN90" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="CO90" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="CP90"/>
       <c r="CQ90" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="CR90"/>
       <c r="CS90"/>
@@ -15077,19 +15077,19 @@
       <c r="CI91"/>
       <c r="CJ91"/>
       <c r="CK91" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="CL91"/>
       <c r="CM91"/>
       <c r="CN91" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="CO91" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="CP91"/>
       <c r="CQ91" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="CR91"/>
       <c r="CS91"/>
@@ -15249,16 +15249,16 @@
       <c r="CI92"/>
       <c r="CJ92"/>
       <c r="CK92" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="CL92"/>
       <c r="CM92"/>
       <c r="CN92" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="CO92"/>
       <c r="CP92" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="CQ92"/>
       <c r="CR92"/>
@@ -15419,16 +15419,16 @@
       <c r="CI93"/>
       <c r="CJ93"/>
       <c r="CK93" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="CL93"/>
       <c r="CM93"/>
       <c r="CN93" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="CO93"/>
       <c r="CP93" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="CQ93"/>
       <c r="CR93"/>
@@ -15589,16 +15589,16 @@
       <c r="CI94"/>
       <c r="CJ94"/>
       <c r="CK94" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="CL94"/>
       <c r="CM94"/>
       <c r="CN94" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="CO94"/>
       <c r="CP94" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="CQ94"/>
       <c r="CR94"/>
@@ -15763,19 +15763,19 @@
       <c r="CI95"/>
       <c r="CJ95"/>
       <c r="CK95" t="n">
-        <v>6.1</v>
+        <v>4.3</v>
       </c>
       <c r="CL95"/>
       <c r="CM95"/>
       <c r="CN95" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="CO95" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="CP95"/>
       <c r="CQ95" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="CR95"/>
       <c r="CS95"/>
@@ -15939,19 +15939,19 @@
       <c r="CI96"/>
       <c r="CJ96"/>
       <c r="CK96" t="n">
-        <v>6.1</v>
+        <v>4.3</v>
       </c>
       <c r="CL96"/>
       <c r="CM96"/>
       <c r="CN96" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="CO96" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="CP96"/>
       <c r="CQ96" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="CR96"/>
       <c r="CS96"/>
@@ -16115,19 +16115,19 @@
       <c r="CI97"/>
       <c r="CJ97"/>
       <c r="CK97" t="n">
-        <v>6.1</v>
+        <v>4.3</v>
       </c>
       <c r="CL97"/>
       <c r="CM97"/>
       <c r="CN97" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="CO97" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="CP97"/>
       <c r="CQ97" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="CR97"/>
       <c r="CS97"/>
@@ -18038,13 +18038,13 @@
       <c r="CL110"/>
       <c r="CM110"/>
       <c r="CN110" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="CO110"/>
       <c r="CP110"/>
       <c r="CQ110"/>
       <c r="CR110" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="CS110"/>
       <c r="CT110"/>
@@ -18208,13 +18208,13 @@
       <c r="CL111"/>
       <c r="CM111"/>
       <c r="CN111" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="CO111"/>
       <c r="CP111"/>
       <c r="CQ111"/>
       <c r="CR111" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="CS111"/>
       <c r="CT111"/>
@@ -18378,13 +18378,13 @@
       <c r="CL112"/>
       <c r="CM112"/>
       <c r="CN112" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="CO112"/>
       <c r="CP112"/>
       <c r="CQ112"/>
       <c r="CR112" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="CS112"/>
       <c r="CT112"/>
@@ -18552,10 +18552,10 @@
       <c r="CL113"/>
       <c r="CM113"/>
       <c r="CN113" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="CO113" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="CP113"/>
       <c r="CQ113"/>
@@ -18728,10 +18728,10 @@
       <c r="CL114"/>
       <c r="CM114"/>
       <c r="CN114" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="CO114" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="CP114"/>
       <c r="CQ114"/>
@@ -18904,10 +18904,10 @@
       <c r="CL115"/>
       <c r="CM115"/>
       <c r="CN115" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="CO115" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="CP115"/>
       <c r="CQ115"/>
@@ -19071,18 +19071,18 @@
       <c r="CI116"/>
       <c r="CJ116"/>
       <c r="CK116" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="CL116"/>
       <c r="CM116"/>
       <c r="CN116" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="CO116"/>
       <c r="CP116"/>
       <c r="CQ116"/>
       <c r="CR116" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="CS116"/>
       <c r="CT116"/>
@@ -19241,18 +19241,18 @@
       <c r="CI117"/>
       <c r="CJ117"/>
       <c r="CK117" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="CL117"/>
       <c r="CM117"/>
       <c r="CN117" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="CO117"/>
       <c r="CP117"/>
       <c r="CQ117"/>
       <c r="CR117" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="CS117"/>
       <c r="CT117"/>
@@ -19411,18 +19411,18 @@
       <c r="CI118"/>
       <c r="CJ118"/>
       <c r="CK118" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="CL118"/>
       <c r="CM118"/>
       <c r="CN118" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="CO118"/>
       <c r="CP118"/>
       <c r="CQ118"/>
       <c r="CR118" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="CS118"/>
       <c r="CT118"/>
@@ -19585,20 +19585,20 @@
       <c r="CI119"/>
       <c r="CJ119"/>
       <c r="CK119" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="CL119"/>
       <c r="CM119"/>
       <c r="CN119" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="CO119" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="CP119"/>
       <c r="CQ119"/>
       <c r="CR119" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="CS119"/>
       <c r="CT119"/>
@@ -19761,20 +19761,20 @@
       <c r="CI120"/>
       <c r="CJ120"/>
       <c r="CK120" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="CL120"/>
       <c r="CM120"/>
       <c r="CN120" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="CO120" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="CP120"/>
       <c r="CQ120"/>
       <c r="CR120" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="CS120"/>
       <c r="CT120"/>
@@ -19937,20 +19937,20 @@
       <c r="CI121"/>
       <c r="CJ121"/>
       <c r="CK121" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="CL121"/>
       <c r="CM121"/>
       <c r="CN121" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="CO121" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="CP121"/>
       <c r="CQ121"/>
       <c r="CR121" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="CS121"/>
       <c r="CT121"/>
@@ -21879,17 +21879,17 @@
       <c r="CI134"/>
       <c r="CJ134"/>
       <c r="CK134" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="CL134"/>
       <c r="CM134"/>
       <c r="CN134" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="CO134"/>
       <c r="CP134"/>
       <c r="CQ134" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="CR134"/>
       <c r="CS134"/>
@@ -22049,17 +22049,17 @@
       <c r="CI135"/>
       <c r="CJ135"/>
       <c r="CK135" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="CL135"/>
       <c r="CM135"/>
       <c r="CN135" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="CO135"/>
       <c r="CP135"/>
       <c r="CQ135" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="CR135"/>
       <c r="CS135"/>
@@ -22219,17 +22219,17 @@
       <c r="CI136"/>
       <c r="CJ136"/>
       <c r="CK136" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="CL136"/>
       <c r="CM136"/>
       <c r="CN136" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="CO136"/>
       <c r="CP136"/>
       <c r="CQ136" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="CR136"/>
       <c r="CS136"/>
@@ -22393,18 +22393,18 @@
       <c r="CI137"/>
       <c r="CJ137"/>
       <c r="CK137" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="CL137"/>
       <c r="CM137"/>
       <c r="CN137" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="CO137" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="CP137" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="CQ137"/>
       <c r="CR137"/>
@@ -22569,18 +22569,18 @@
       <c r="CI138"/>
       <c r="CJ138"/>
       <c r="CK138" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="CL138"/>
       <c r="CM138"/>
       <c r="CN138" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="CO138" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="CP138" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="CQ138"/>
       <c r="CR138"/>
@@ -22745,18 +22745,18 @@
       <c r="CI139"/>
       <c r="CJ139"/>
       <c r="CK139" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="CL139"/>
       <c r="CM139"/>
       <c r="CN139" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="CO139" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="CP139" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="CQ139"/>
       <c r="CR139"/>
@@ -22917,12 +22917,12 @@
       <c r="CI140"/>
       <c r="CJ140"/>
       <c r="CK140" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="CL140"/>
       <c r="CM140"/>
       <c r="CN140" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="CO140"/>
       <c r="CP140"/>
@@ -23087,12 +23087,12 @@
       <c r="CI141"/>
       <c r="CJ141"/>
       <c r="CK141" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="CL141"/>
       <c r="CM141"/>
       <c r="CN141" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="CO141"/>
       <c r="CP141"/>
@@ -23257,12 +23257,12 @@
       <c r="CI142"/>
       <c r="CJ142"/>
       <c r="CK142" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="CL142"/>
       <c r="CM142"/>
       <c r="CN142" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="CO142"/>
       <c r="CP142"/>
@@ -23431,18 +23431,18 @@
       <c r="CI143"/>
       <c r="CJ143"/>
       <c r="CK143" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="CL143"/>
       <c r="CM143"/>
       <c r="CN143" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="CO143" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="CP143" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="CQ143"/>
       <c r="CR143"/>
@@ -23607,18 +23607,18 @@
       <c r="CI144"/>
       <c r="CJ144"/>
       <c r="CK144" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="CL144"/>
       <c r="CM144"/>
       <c r="CN144" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="CO144" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="CP144" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="CQ144"/>
       <c r="CR144"/>
@@ -23783,18 +23783,18 @@
       <c r="CI145"/>
       <c r="CJ145"/>
       <c r="CK145" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="CL145"/>
       <c r="CM145"/>
       <c r="CN145" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="CO145" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="CP145" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="CQ145"/>
       <c r="CR145"/>
@@ -25753,21 +25753,21 @@
       <c r="CI158"/>
       <c r="CJ158"/>
       <c r="CK158" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="CL158"/>
       <c r="CM158"/>
       <c r="CN158" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="CO158"/>
       <c r="CP158" t="n">
-        <v>31.9</v>
+        <v>3.5</v>
       </c>
       <c r="CQ158"/>
       <c r="CR158"/>
       <c r="CS158" t="n">
-        <v>32.8</v>
+        <v>2.8</v>
       </c>
       <c r="CT158"/>
       <c r="CU158"/>
@@ -25929,21 +25929,21 @@
       <c r="CI159"/>
       <c r="CJ159"/>
       <c r="CK159" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="CL159"/>
       <c r="CM159"/>
       <c r="CN159" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="CO159"/>
       <c r="CP159" t="n">
-        <v>31.9</v>
+        <v>3.5</v>
       </c>
       <c r="CQ159"/>
       <c r="CR159"/>
       <c r="CS159" t="n">
-        <v>32.8</v>
+        <v>2.8</v>
       </c>
       <c r="CT159"/>
       <c r="CU159"/>
@@ -26105,21 +26105,21 @@
       <c r="CI160"/>
       <c r="CJ160"/>
       <c r="CK160" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="CL160"/>
       <c r="CM160"/>
       <c r="CN160" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="CO160"/>
       <c r="CP160" t="n">
-        <v>31.9</v>
+        <v>3.5</v>
       </c>
       <c r="CQ160"/>
       <c r="CR160"/>
       <c r="CS160" t="n">
-        <v>32.8</v>
+        <v>2.8</v>
       </c>
       <c r="CT160"/>
       <c r="CU160"/>
@@ -26281,21 +26281,21 @@
       <c r="CI161"/>
       <c r="CJ161"/>
       <c r="CK161" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="CL161"/>
       <c r="CM161"/>
       <c r="CN161" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="CO161" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="CP161"/>
       <c r="CQ161"/>
       <c r="CR161"/>
       <c r="CS161" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="CT161"/>
       <c r="CU161"/>
@@ -26457,21 +26457,21 @@
       <c r="CI162"/>
       <c r="CJ162"/>
       <c r="CK162" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="CL162"/>
       <c r="CM162"/>
       <c r="CN162" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="CO162" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="CP162"/>
       <c r="CQ162"/>
       <c r="CR162"/>
       <c r="CS162" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="CT162"/>
       <c r="CU162"/>
@@ -26633,21 +26633,21 @@
       <c r="CI163"/>
       <c r="CJ163"/>
       <c r="CK163" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="CL163"/>
       <c r="CM163"/>
       <c r="CN163" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="CO163" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="CP163"/>
       <c r="CQ163"/>
       <c r="CR163"/>
       <c r="CS163" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="CT163"/>
       <c r="CU163"/>
@@ -26809,21 +26809,21 @@
       <c r="CI164"/>
       <c r="CJ164"/>
       <c r="CK164" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="CL164"/>
       <c r="CM164"/>
       <c r="CN164" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="CO164"/>
       <c r="CP164" t="n">
-        <v>2.1</v>
+        <v>14.1</v>
       </c>
       <c r="CQ164"/>
       <c r="CR164"/>
       <c r="CS164" t="n">
-        <v>3.7</v>
+        <v>16.2</v>
       </c>
       <c r="CT164"/>
       <c r="CU164"/>
@@ -26985,21 +26985,21 @@
       <c r="CI165"/>
       <c r="CJ165"/>
       <c r="CK165" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="CL165"/>
       <c r="CM165"/>
       <c r="CN165" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="CO165"/>
       <c r="CP165" t="n">
-        <v>2.1</v>
+        <v>14.1</v>
       </c>
       <c r="CQ165"/>
       <c r="CR165"/>
       <c r="CS165" t="n">
-        <v>3.7</v>
+        <v>16.2</v>
       </c>
       <c r="CT165"/>
       <c r="CU165"/>
@@ -27161,21 +27161,21 @@
       <c r="CI166"/>
       <c r="CJ166"/>
       <c r="CK166" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="CL166"/>
       <c r="CM166"/>
       <c r="CN166" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="CO166"/>
       <c r="CP166" t="n">
-        <v>2.1</v>
+        <v>14.1</v>
       </c>
       <c r="CQ166"/>
       <c r="CR166"/>
       <c r="CS166" t="n">
-        <v>3.7</v>
+        <v>16.2</v>
       </c>
       <c r="CT166"/>
       <c r="CU166"/>
@@ -27337,21 +27337,21 @@
       <c r="CI167"/>
       <c r="CJ167"/>
       <c r="CK167" t="n">
-        <v>5.5</v>
+        <v>42.6</v>
       </c>
       <c r="CL167"/>
       <c r="CM167"/>
       <c r="CN167" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="CO167" t="n">
-        <v>5.1</v>
+        <v>49.4</v>
       </c>
       <c r="CP167"/>
       <c r="CQ167"/>
       <c r="CR167"/>
       <c r="CS167" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="CT167"/>
       <c r="CU167"/>
@@ -27513,21 +27513,21 @@
       <c r="CI168"/>
       <c r="CJ168"/>
       <c r="CK168" t="n">
-        <v>5.5</v>
+        <v>42.6</v>
       </c>
       <c r="CL168"/>
       <c r="CM168"/>
       <c r="CN168" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="CO168" t="n">
-        <v>5.1</v>
+        <v>49.4</v>
       </c>
       <c r="CP168"/>
       <c r="CQ168"/>
       <c r="CR168"/>
       <c r="CS168" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="CT168"/>
       <c r="CU168"/>
@@ -27689,21 +27689,21 @@
       <c r="CI169"/>
       <c r="CJ169"/>
       <c r="CK169" t="n">
-        <v>5.5</v>
+        <v>42.6</v>
       </c>
       <c r="CL169"/>
       <c r="CM169"/>
       <c r="CN169" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="CO169" t="n">
-        <v>5.1</v>
+        <v>49.4</v>
       </c>
       <c r="CP169"/>
       <c r="CQ169"/>
       <c r="CR169"/>
       <c r="CS169" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="CT169"/>
       <c r="CU169"/>
@@ -29641,21 +29641,21 @@
       <c r="CI182"/>
       <c r="CJ182"/>
       <c r="CK182" t="n">
-        <v>3.9</v>
+        <v>8.2</v>
       </c>
       <c r="CL182"/>
       <c r="CM182"/>
       <c r="CN182" t="n">
-        <v>9</v>
+        <v>13.4</v>
       </c>
       <c r="CO182"/>
       <c r="CP182"/>
       <c r="CQ182"/>
       <c r="CR182" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="CS182" t="n">
-        <v>8.3</v>
+        <v>6.9</v>
       </c>
       <c r="CT182"/>
       <c r="CU182"/>
@@ -29817,21 +29817,21 @@
       <c r="CI183"/>
       <c r="CJ183"/>
       <c r="CK183" t="n">
-        <v>3.9</v>
+        <v>8.2</v>
       </c>
       <c r="CL183"/>
       <c r="CM183"/>
       <c r="CN183" t="n">
-        <v>9</v>
+        <v>13.4</v>
       </c>
       <c r="CO183"/>
       <c r="CP183"/>
       <c r="CQ183"/>
       <c r="CR183" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="CS183" t="n">
-        <v>8.3</v>
+        <v>6.9</v>
       </c>
       <c r="CT183"/>
       <c r="CU183"/>
@@ -29993,21 +29993,21 @@
       <c r="CI184"/>
       <c r="CJ184"/>
       <c r="CK184" t="n">
-        <v>3.9</v>
+        <v>8.2</v>
       </c>
       <c r="CL184"/>
       <c r="CM184"/>
       <c r="CN184" t="n">
-        <v>9</v>
+        <v>13.4</v>
       </c>
       <c r="CO184"/>
       <c r="CP184"/>
       <c r="CQ184"/>
       <c r="CR184" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="CS184" t="n">
-        <v>8.3</v>
+        <v>6.9</v>
       </c>
       <c r="CT184"/>
       <c r="CU184"/>
@@ -30169,21 +30169,21 @@
       <c r="CI185"/>
       <c r="CJ185"/>
       <c r="CK185" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="CL185"/>
       <c r="CM185"/>
       <c r="CN185" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="CO185" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="CP185"/>
       <c r="CQ185"/>
       <c r="CR185"/>
       <c r="CS185" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="CT185"/>
       <c r="CU185"/>
@@ -30345,21 +30345,21 @@
       <c r="CI186"/>
       <c r="CJ186"/>
       <c r="CK186" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="CL186"/>
       <c r="CM186"/>
       <c r="CN186" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="CO186" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="CP186"/>
       <c r="CQ186"/>
       <c r="CR186"/>
       <c r="CS186" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="CT186"/>
       <c r="CU186"/>
@@ -30521,21 +30521,21 @@
       <c r="CI187"/>
       <c r="CJ187"/>
       <c r="CK187" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="CL187"/>
       <c r="CM187"/>
       <c r="CN187" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="CO187" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="CP187"/>
       <c r="CQ187"/>
       <c r="CR187"/>
       <c r="CS187" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="CT187"/>
       <c r="CU187"/>
@@ -30697,21 +30697,21 @@
       <c r="CI188"/>
       <c r="CJ188"/>
       <c r="CK188" t="n">
-        <v>26.2</v>
+        <v>7.9</v>
       </c>
       <c r="CL188"/>
       <c r="CM188"/>
       <c r="CN188" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="CO188"/>
       <c r="CP188"/>
       <c r="CQ188"/>
       <c r="CR188" t="n">
-        <v>18.9</v>
+        <v>5.5</v>
       </c>
       <c r="CS188" t="n">
-        <v>10.9</v>
+        <v>1.9</v>
       </c>
       <c r="CT188"/>
       <c r="CU188"/>
@@ -30873,21 +30873,21 @@
       <c r="CI189"/>
       <c r="CJ189"/>
       <c r="CK189" t="n">
-        <v>26.2</v>
+        <v>7.9</v>
       </c>
       <c r="CL189"/>
       <c r="CM189"/>
       <c r="CN189" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="CO189"/>
       <c r="CP189"/>
       <c r="CQ189"/>
       <c r="CR189" t="n">
-        <v>18.9</v>
+        <v>5.5</v>
       </c>
       <c r="CS189" t="n">
-        <v>10.9</v>
+        <v>1.9</v>
       </c>
       <c r="CT189"/>
       <c r="CU189"/>
@@ -31049,21 +31049,21 @@
       <c r="CI190"/>
       <c r="CJ190"/>
       <c r="CK190" t="n">
-        <v>26.2</v>
+        <v>7.9</v>
       </c>
       <c r="CL190"/>
       <c r="CM190"/>
       <c r="CN190" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="CO190"/>
       <c r="CP190"/>
       <c r="CQ190"/>
       <c r="CR190" t="n">
-        <v>18.9</v>
+        <v>5.5</v>
       </c>
       <c r="CS190" t="n">
-        <v>10.9</v>
+        <v>1.9</v>
       </c>
       <c r="CT190"/>
       <c r="CU190"/>
@@ -31225,21 +31225,21 @@
       <c r="CI191"/>
       <c r="CJ191"/>
       <c r="CK191" t="n">
-        <v>34.6</v>
+        <v>81.9</v>
       </c>
       <c r="CL191"/>
       <c r="CM191"/>
       <c r="CN191" t="n">
-        <v>6.7</v>
+        <v>5.7</v>
       </c>
       <c r="CO191" t="n">
-        <v>54.3</v>
+        <v>92.2</v>
       </c>
       <c r="CP191"/>
       <c r="CQ191"/>
       <c r="CR191"/>
       <c r="CS191" t="n">
-        <v>8.4</v>
+        <v>11.2</v>
       </c>
       <c r="CT191"/>
       <c r="CU191"/>
@@ -31401,21 +31401,21 @@
       <c r="CI192"/>
       <c r="CJ192"/>
       <c r="CK192" t="n">
-        <v>34.6</v>
+        <v>81.9</v>
       </c>
       <c r="CL192"/>
       <c r="CM192"/>
       <c r="CN192" t="n">
-        <v>6.7</v>
+        <v>5.7</v>
       </c>
       <c r="CO192" t="n">
-        <v>54.3</v>
+        <v>92.2</v>
       </c>
       <c r="CP192"/>
       <c r="CQ192"/>
       <c r="CR192"/>
       <c r="CS192" t="n">
-        <v>8.4</v>
+        <v>11.2</v>
       </c>
       <c r="CT192"/>
       <c r="CU192"/>
@@ -31577,21 +31577,21 @@
       <c r="CI193"/>
       <c r="CJ193"/>
       <c r="CK193" t="n">
-        <v>34.6</v>
+        <v>81.9</v>
       </c>
       <c r="CL193"/>
       <c r="CM193"/>
       <c r="CN193" t="n">
-        <v>6.7</v>
+        <v>5.7</v>
       </c>
       <c r="CO193" t="n">
-        <v>54.3</v>
+        <v>92.2</v>
       </c>
       <c r="CP193"/>
       <c r="CQ193"/>
       <c r="CR193"/>
       <c r="CS193" t="n">
-        <v>8.4</v>
+        <v>11.2</v>
       </c>
       <c r="CT193"/>
       <c r="CU193"/>
@@ -33541,21 +33541,21 @@
       <c r="CI206"/>
       <c r="CJ206"/>
       <c r="CK206" t="n">
-        <v>8.3</v>
+        <v>6</v>
       </c>
       <c r="CL206"/>
       <c r="CM206"/>
       <c r="CN206" t="n">
-        <v>24.7</v>
+        <v>6.1</v>
       </c>
       <c r="CO206"/>
       <c r="CP206"/>
       <c r="CQ206" t="n">
-        <v>267.7</v>
+        <v>13.4</v>
       </c>
       <c r="CR206"/>
       <c r="CS206" t="n">
-        <v>211.8</v>
+        <v>10.5</v>
       </c>
       <c r="CT206"/>
       <c r="CU206"/>
@@ -33717,21 +33717,21 @@
       <c r="CI207"/>
       <c r="CJ207"/>
       <c r="CK207" t="n">
-        <v>8.3</v>
+        <v>6</v>
       </c>
       <c r="CL207"/>
       <c r="CM207"/>
       <c r="CN207" t="n">
-        <v>24.7</v>
+        <v>6.1</v>
       </c>
       <c r="CO207"/>
       <c r="CP207"/>
       <c r="CQ207" t="n">
-        <v>267.7</v>
+        <v>13.4</v>
       </c>
       <c r="CR207"/>
       <c r="CS207" t="n">
-        <v>211.8</v>
+        <v>10.5</v>
       </c>
       <c r="CT207"/>
       <c r="CU207"/>
@@ -33893,21 +33893,21 @@
       <c r="CI208"/>
       <c r="CJ208"/>
       <c r="CK208" t="n">
-        <v>8.3</v>
+        <v>6</v>
       </c>
       <c r="CL208"/>
       <c r="CM208"/>
       <c r="CN208" t="n">
-        <v>24.7</v>
+        <v>6.1</v>
       </c>
       <c r="CO208"/>
       <c r="CP208"/>
       <c r="CQ208" t="n">
-        <v>267.7</v>
+        <v>13.4</v>
       </c>
       <c r="CR208"/>
       <c r="CS208" t="n">
-        <v>211.8</v>
+        <v>10.5</v>
       </c>
       <c r="CT208"/>
       <c r="CU208"/>
@@ -34069,21 +34069,21 @@
       <c r="CI209"/>
       <c r="CJ209"/>
       <c r="CK209" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="CL209"/>
       <c r="CM209"/>
       <c r="CN209" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="CO209" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="CP209"/>
       <c r="CQ209"/>
       <c r="CR209"/>
       <c r="CS209" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="CT209"/>
       <c r="CU209"/>
@@ -34245,21 +34245,21 @@
       <c r="CI210"/>
       <c r="CJ210"/>
       <c r="CK210" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="CL210"/>
       <c r="CM210"/>
       <c r="CN210" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="CO210" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="CP210"/>
       <c r="CQ210"/>
       <c r="CR210"/>
       <c r="CS210" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="CT210"/>
       <c r="CU210"/>
@@ -34421,21 +34421,21 @@
       <c r="CI211"/>
       <c r="CJ211"/>
       <c r="CK211" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="CL211"/>
       <c r="CM211"/>
       <c r="CN211" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="CO211" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="CP211"/>
       <c r="CQ211"/>
       <c r="CR211"/>
       <c r="CS211" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="CT211"/>
       <c r="CU211"/>
@@ -34597,21 +34597,21 @@
       <c r="CI212"/>
       <c r="CJ212"/>
       <c r="CK212" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="CL212"/>
       <c r="CM212"/>
       <c r="CN212" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="CO212"/>
       <c r="CP212"/>
       <c r="CQ212" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="CR212"/>
       <c r="CS212" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="CT212"/>
       <c r="CU212"/>
@@ -34773,21 +34773,21 @@
       <c r="CI213"/>
       <c r="CJ213"/>
       <c r="CK213" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="CL213"/>
       <c r="CM213"/>
       <c r="CN213" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="CO213"/>
       <c r="CP213"/>
       <c r="CQ213" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="CR213"/>
       <c r="CS213" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="CT213"/>
       <c r="CU213"/>
@@ -34949,21 +34949,21 @@
       <c r="CI214"/>
       <c r="CJ214"/>
       <c r="CK214" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="CL214"/>
       <c r="CM214"/>
       <c r="CN214" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="CO214"/>
       <c r="CP214"/>
       <c r="CQ214" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="CR214"/>
       <c r="CS214" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="CT214"/>
       <c r="CU214"/>
@@ -35125,21 +35125,21 @@
       <c r="CI215"/>
       <c r="CJ215"/>
       <c r="CK215" t="n">
-        <v>76.3</v>
+        <v>82.3</v>
       </c>
       <c r="CL215"/>
       <c r="CM215"/>
       <c r="CN215" t="n">
-        <v>4.1</v>
+        <v>10.7</v>
       </c>
       <c r="CO215" t="n">
-        <v>84.8</v>
+        <v>110.9</v>
       </c>
       <c r="CP215"/>
       <c r="CQ215"/>
       <c r="CR215"/>
       <c r="CS215" t="n">
-        <v>13.4</v>
+        <v>10.5</v>
       </c>
       <c r="CT215"/>
       <c r="CU215"/>
@@ -35301,21 +35301,21 @@
       <c r="CI216"/>
       <c r="CJ216"/>
       <c r="CK216" t="n">
-        <v>76.3</v>
+        <v>82.3</v>
       </c>
       <c r="CL216"/>
       <c r="CM216"/>
       <c r="CN216" t="n">
-        <v>4.1</v>
+        <v>10.7</v>
       </c>
       <c r="CO216" t="n">
-        <v>84.8</v>
+        <v>110.9</v>
       </c>
       <c r="CP216"/>
       <c r="CQ216"/>
       <c r="CR216"/>
       <c r="CS216" t="n">
-        <v>13.4</v>
+        <v>10.5</v>
       </c>
       <c r="CT216"/>
       <c r="CU216"/>
@@ -35477,21 +35477,21 @@
       <c r="CI217"/>
       <c r="CJ217"/>
       <c r="CK217" t="n">
-        <v>76.3</v>
+        <v>82.3</v>
       </c>
       <c r="CL217"/>
       <c r="CM217"/>
       <c r="CN217" t="n">
-        <v>4.1</v>
+        <v>10.7</v>
       </c>
       <c r="CO217" t="n">
-        <v>84.8</v>
+        <v>110.9</v>
       </c>
       <c r="CP217"/>
       <c r="CQ217"/>
       <c r="CR217"/>
       <c r="CS217" t="n">
-        <v>13.4</v>
+        <v>10.5</v>
       </c>
       <c r="CT217"/>
       <c r="CU217"/>
